--- a/backend/excel-templates/student_users_template.xlsx
+++ b/backend/excel-templates/student_users_template.xlsx
@@ -398,6 +398,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G3"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,30 +451,30 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>MASTER</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>student.example@pcampus.edu.np</v>
+        <v>ram.sharma@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C3" t="str">
-        <v>Narayan</v>
+        <v>Ram</v>
       </c>
       <c r="D3" t="str">
-        <v>Bhandari</v>
+        <v>Sharma</v>
       </c>
       <c r="E3" t="str">
-        <v>080MSNCS01</v>
+        <v>078BCT001</v>
       </c>
       <c r="F3" t="str">
-        <v>MSNCS</v>
+        <v>BCT</v>
       </c>
       <c r="G3" t="str">
-        <v>MASTER</v>
+        <v>BACHELOR</v>
       </c>
     </row>
   </sheetData>

--- a/backend/excel-templates/student_users_template.xlsx
+++ b/backend/excel-templates/student_users_template.xlsx
@@ -398,15 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G3"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -451,30 +442,30 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>MASTER</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ram.sharma@pcampus.edu.np</v>
+        <v>student.example@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
-        <v>subesh</v>
+        <v>pass123</v>
       </c>
       <c r="C3" t="str">
-        <v>Ram</v>
+        <v>Narayan</v>
       </c>
       <c r="D3" t="str">
-        <v>Sharma</v>
+        <v>Bhandari</v>
       </c>
       <c r="E3" t="str">
-        <v>078BCT001</v>
+        <v>080MSNCS01</v>
       </c>
       <c r="F3" t="str">
-        <v>BCT</v>
+        <v>MSNCS</v>
       </c>
       <c r="G3" t="str">
-        <v>BACHELOR</v>
+        <v>MASTER</v>
       </c>
     </row>
   </sheetData>
